--- a/output.xlsx
+++ b/output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X43"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,16 +552,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68841</v>
+        <v>68884</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>樂庵類稿</t>
+          <t>復庵草</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>le an lei gao</t>
+          <t>fu an cao</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -583,7 +583,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V2" t="inlineStr"/>
@@ -612,16 +612,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68842</v>
+        <v>68885</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>嗜泉詩存</t>
+          <t>經脈圖曜</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>shi quan shi cun</t>
+          <t>jing mai tu yao</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -643,7 +643,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V3" t="inlineStr"/>
@@ -672,16 +672,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68843</v>
+        <v>68886</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>西村詩集</t>
+          <t>本草補遺</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>xi cun shi ji</t>
+          <t>ben cao bu yi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -696,14 +696,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V4" t="inlineStr"/>
@@ -732,16 +732,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68844</v>
+        <v>68887</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>斲冰集</t>
+          <t>格物輯略</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>zhuo bing ji</t>
+          <t>ge wu ji lve</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -756,14 +756,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -792,16 +792,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68845</v>
+        <v>68888</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>易疑詩疑</t>
+          <t>鄕黨攷略一卷</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>yi yi shi yi</t>
+          <t>xiang dang kao lve yi juan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -823,7 +823,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V6" t="inlineStr"/>
@@ -852,16 +852,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>68846</v>
+        <v>68889</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>个亭集</t>
+          <t>名醫類案</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ge ting ji</t>
+          <t>ming yi lei an</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -876,14 +876,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V7" t="inlineStr"/>
@@ -912,16 +912,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>68847</v>
+        <v>68890</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>莧園集</t>
+          <t>治肝三法</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>xian yuan ji</t>
+          <t>zhi gan san fa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -936,14 +936,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V8" t="inlineStr"/>
@@ -972,16 +972,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>68848</v>
+        <v>68891</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>浣筆池藏稿</t>
+          <t>傷寒易知</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>huan bi chi cang gao</t>
+          <t>shang han yi zhi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -996,14 +996,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V9" t="inlineStr"/>
@@ -1032,16 +1032,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68849</v>
+        <v>68892</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>侖者菑</t>
+          <t>醫案心法</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lun zhe zai</t>
+          <t>yi an xin fa</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V10" t="inlineStr"/>
@@ -1092,16 +1092,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68850</v>
+        <v>68893</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>勿个集</t>
+          <t>翼如詩文集</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>wu ge ji</t>
+          <t>yi ru shi wen ji</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1123,7 +1123,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V11" t="inlineStr"/>
@@ -1152,16 +1152,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68851</v>
+        <v>68894</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>寤歌室集</t>
+          <t>綠天樓詩文八卷</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wu ge shi ji</t>
+          <t>lv tian lou shi wen ba juan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1176,14 +1176,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V12" t="inlineStr"/>
@@ -1212,16 +1212,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>68852</v>
+        <v>68895</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>𣏌憂草</t>
+          <t>欹枕憶游草</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>𣏌 you cao</t>
+          <t>yi zhen yi you cao</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V13" t="inlineStr"/>
@@ -1272,16 +1272,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>68853</v>
+        <v>68896</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>正氣集</t>
+          <t>形家五要補編</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>zheng qi ji</t>
+          <t>xing jia wu yao bu bian</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1296,14 +1296,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V14" t="inlineStr"/>
@@ -1332,16 +1332,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>68854</v>
+        <v>68897</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>梅癡集稿</t>
+          <t>古今名方摘要</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mei chi ji gao</t>
+          <t>gu jin ming fang zhai yao</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1356,14 +1356,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V15" t="inlineStr"/>
@@ -1392,16 +1392,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>68855</v>
+        <v>68898</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>蘗亭鳴稿</t>
+          <t>內傷論</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bo ting ming gao</t>
+          <t>nei shang lun</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1416,14 +1416,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V16" t="inlineStr"/>
@@ -1452,16 +1452,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>68856</v>
+        <v>68899</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>四書不夜篇二十卷</t>
+          <t>金匱述</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>si shu bu ye pian er shi juan</t>
+          <t>jin gui shu</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1483,7 +1483,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V17" t="inlineStr"/>
@@ -1512,16 +1512,16 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>68857</v>
+        <v>68900</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周易然犀五卷</t>
+          <t>奇痢症述</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>zhou yi ran xi wu juan</t>
+          <t>qi li zheng shu</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1543,7 +1543,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V18" t="inlineStr"/>
@@ -1572,16 +1572,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>68858</v>
+        <v>68901</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>三才匯璧四卷</t>
+          <t>醫案賞</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>san cai hui bi si juan</t>
+          <t>yi an shang</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1603,7 +1603,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V19" t="inlineStr"/>
@@ -1632,16 +1632,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>68859</v>
+        <v>68902</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>醫學指南十卷</t>
+          <t>歌勞倦</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>yi xue zhi nan shi juan</t>
+          <t>ge lao juan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1663,7 +1663,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V20" t="inlineStr"/>
@@ -1692,16 +1692,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>68860</v>
+        <v>68903</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>元科秘要四卷</t>
+          <t>高陽山人詩稿</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>yuan ke mi yao si juan</t>
+          <t>gao yang shan ren shi gao</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1716,14 +1716,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V21" t="inlineStr"/>
@@ -1752,16 +1752,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>68861</v>
+        <v>68904</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>經騐良方十二卷</t>
+          <t>無隅館集</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jing yan liang fang shi er juan</t>
+          <t>wu yu guan ji</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1776,14 +1776,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V22" t="inlineStr"/>
@@ -1812,16 +1812,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>68862</v>
+        <v>68905</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>幼幼心法二卷</t>
+          <t>地理擷華</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>you you xin fa er juan</t>
+          <t>di li xie hua</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1843,7 +1843,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V23" t="inlineStr"/>
@@ -1872,16 +1872,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>68863</v>
+        <v>68906</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>元修最上乘二卷</t>
+          <t>地理辨非</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>yuan xiu zui shang cheng er juan</t>
+          <t>di li bian fei</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1903,7 +1903,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V24" t="inlineStr"/>
@@ -1932,16 +1932,16 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>68864</v>
+        <v>68907</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>自懲要則</t>
+          <t>地理辨正疏</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>zi cheng yao ze</t>
+          <t>di li bian zheng shu</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V25" t="inlineStr"/>
@@ -1992,16 +1992,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>68865</v>
+        <v>68908</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>裴子言醫</t>
+          <t>四知堂詩稿</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pei zi yan yi</t>
+          <t>si zhi tang shi gao</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V26" t="inlineStr"/>
@@ -2052,16 +2052,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>68866</v>
+        <v>68909</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>刪潤原病式</t>
+          <t>證治集腋十卷</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>shan run yuan bing shi</t>
+          <t>zheng zhi ji ye shi juan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V27" t="inlineStr"/>
@@ -2112,16 +2112,16 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>68867</v>
+        <v>68910</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>學圃堂集</t>
+          <t>醫方歌訣六卷</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>xue pu tang ji</t>
+          <t>yi fang ge jue liu juan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2136,7 +2136,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V28" t="inlineStr"/>
@@ -2172,16 +2172,16 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>68868</v>
+        <v>68911</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>耕餘集</t>
+          <t>本草補註六卷</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>geng yu ji</t>
+          <t>ben cao bu zhu liu juan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2196,7 +2196,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V29" t="inlineStr"/>
@@ -2232,16 +2232,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>68869</v>
+        <v>68912</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>捫䣛軒詩草</t>
+          <t>楞香詩草</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>men qi xuan shi cao</t>
+          <t>leng xiang shi cao</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V30" t="inlineStr"/>
@@ -2292,16 +2292,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>68870</v>
+        <v>68913</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>侜浦詩鈔</t>
+          <t>自訟日鈔</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>zhou pu shi chao</t>
+          <t>zi song ri chao</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V31" t="inlineStr"/>
@@ -2352,16 +2352,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>68871</v>
+        <v>68914</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>傷寒家秘心法</t>
+          <t>人身譜</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>shang han jia mi xin fa</t>
+          <t>ren shen pu</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V32" t="inlineStr"/>
@@ -2412,16 +2412,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>68872</v>
+        <v>68915</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>小兒正蒙</t>
+          <t>方歌集論</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>xiao er zheng meng</t>
+          <t>fang ge ji lun</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V33" t="inlineStr"/>
@@ -2472,16 +2472,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>68873</v>
+        <v>68916</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>藥性辨疑</t>
+          <t>本草分劑</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>yao xing bian yi</t>
+          <t>ben cao fen ji</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2503,7 +2503,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V34" t="inlineStr"/>
@@ -2532,16 +2532,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>68874</v>
+        <v>68917</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>明醫會要</t>
+          <t>五經句讀音義考</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ming yi hui yao</t>
+          <t>wu jing ju du yin yi kao</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2563,7 +2563,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V35" t="inlineStr"/>
@@ -2592,16 +2592,16 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>68875</v>
+        <v>68918</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>醫經大旨</t>
+          <t>唐宋詩摘錦</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yi jing da zhi</t>
+          <t>tang song shi zhai jin</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2623,7 +2623,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V36" t="inlineStr"/>
@@ -2652,16 +2652,16 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>68876</v>
+        <v>68919</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>診脈家寶</t>
+          <t>生庵讀史錄</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>zhen mai jia bao</t>
+          <t>sheng an du shi lu</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2683,7 +2683,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V37" t="inlineStr"/>
@@ -2712,16 +2712,16 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>68877</v>
+        <v>68920</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>藥性準繩</t>
+          <t>紅豆集</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>yao xing zhun sheng</t>
+          <t>hong dou ji</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2736,14 +2736,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V38" t="inlineStr"/>
@@ -2772,16 +2772,16 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>68878</v>
+        <v>68921</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>卜經一卷</t>
+          <t>石刻蘭亭樂毅論十三行臨本</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bo jing yi juan</t>
+          <t>shi ke lan ting le yi lun shi san xing lin ben</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2803,7 +2803,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V39" t="inlineStr"/>
@@ -2832,16 +2832,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>68879</v>
+        <v>68922</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>傷寒五法</t>
+          <t>葑汀稿</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>shang han wu fa</t>
+          <t>feng ting gao</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V40" t="inlineStr"/>
@@ -2892,16 +2892,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>68880</v>
+        <v>68923</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>證治百問</t>
+          <t>寓廬稿</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>zheng zhi bai wen</t>
+          <t>yu lu gao</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2916,7 +2916,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V41" t="inlineStr"/>
@@ -2952,16 +2952,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>68881</v>
+        <v>68924</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>新方八法</t>
+          <t>東武稿</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>xin fang ba fa</t>
+          <t>dong wu gao</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2976,7 +2976,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V42" t="inlineStr"/>
@@ -3012,16 +3012,16 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>68882</v>
+        <v>68925</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>玉倉詩鈔</t>
+          <t>自怡集</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>yu cang shi chao</t>
+          <t>zi yi ji</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -3036,19 +3036,19 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>68002</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
@@ -3063,12 +3063,852 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>20251003</t>
+          <t>20251010</t>
         </is>
       </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>68926</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>藥塢集</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>yao wu ji</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>68927</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>史論三十卷</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>shi lun san shi juan</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>68928</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>史辨三十卷</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>shi bian san shi juan</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>68929</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>元史攷誤四十卷</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>yuan shi kao wu si shi juan</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>68930</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>懷春小草</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>huai chun xiao cao</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>68931</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>望虞山人全集</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>wang yu shan ren quan ji</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>68932</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>借竹軒稿</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>jie zhu xuan gao</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>68933</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>麗情雜錄</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>li qing za lu</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>68934</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>雪堂初稿</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>xue tang chu gao</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>68935</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>雪堂續稿</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>xue tang xu gao</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>68936</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>足庵集</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>zu an ji</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>68937</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>僧廬集</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>seng lu ji</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>68938</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>抱瑟草堂詩集</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bao se cao tang shi ji</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>68939</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>龍興慈記一卷</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>long xing ci ji yi juan</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>68002</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>20251010</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
